--- a/Data/EXCEL/Transfer/salemon/202208/6541-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6541-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5214E0FF-E691-474B-821B-27A080A0E23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5373663B-8D73-45AA-AA60-A120F7DE3007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6541-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,20 +1226,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
-    <col min="2" max="5" width="9.125" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="8.75" customWidth="1"/>
-    <col min="11" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="9.125" customWidth="1"/>
-    <col min="15" max="15" width="8.75" customWidth="1"/>
-    <col min="16" max="16" width="10.5" customWidth="1"/>
-    <col min="17" max="17" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="5" width="13.125" customWidth="1"/>
+    <col min="6" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="13" width="15" customWidth="1"/>
+    <col min="14" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,105 +1390,105 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>66.900000000000006</v>
+        <v>57.6</v>
       </c>
       <c r="C5" s="7">
-        <v>64</v>
+        <v>52.7</v>
       </c>
       <c r="D5" s="7">
-        <v>71.7</v>
+        <v>57.6</v>
       </c>
       <c r="E5" s="7">
-        <v>60.5</v>
+        <v>45.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-3.3</v>
+        <v>-11.3</v>
       </c>
       <c r="G5" s="8">
-        <v>-4.9000000000000004</v>
+        <v>-17.66</v>
       </c>
       <c r="H5" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="I5" s="8">
-        <v>-42.8</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>17</v>
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="I5" s="10">
+        <v>581.1</v>
+      </c>
+      <c r="J5" s="10">
+        <v>594.5</v>
       </c>
       <c r="K5" s="9">
-        <v>6.7400000000000002E-2</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>17</v>
+        <v>0.106</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1798</v>
       </c>
       <c r="M5" s="9">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="N5" s="8">
-        <v>-42.8</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>17</v>
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="N5" s="10">
+        <v>581.1</v>
+      </c>
+      <c r="O5" s="10">
+        <v>594.5</v>
       </c>
       <c r="P5" s="9">
-        <v>6.7400000000000002E-2</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>17</v>
+        <v>0.106</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>1798</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>55</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="C6" s="7">
-        <v>67.3</v>
+        <v>64</v>
       </c>
       <c r="D6" s="7">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="E6" s="7">
-        <v>52</v>
-      </c>
-      <c r="F6" s="10">
-        <v>12.1</v>
-      </c>
-      <c r="G6" s="10">
-        <v>21.92</v>
+        <v>60.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-3.3</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-4.9000000000000004</v>
       </c>
       <c r="H6" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="I6" s="10">
-        <v>49.6</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="I6" s="8">
+        <v>-42.8</v>
       </c>
       <c r="J6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="9">
-        <v>6.1699999999999998E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="L6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M6" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="N6" s="10">
-        <v>49.6</v>
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="N6" s="8">
+        <v>-42.8</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P6" s="9">
-        <v>6.1699999999999998E-2</v>
+        <v>6.7400000000000002E-2</v>
       </c>
       <c r="Q6" s="9" t="s">
         <v>17</v>
@@ -1490,52 +1496,52 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>55.8</v>
+        <v>55</v>
       </c>
       <c r="C7" s="7">
-        <v>55.2</v>
+        <v>67.3</v>
       </c>
       <c r="D7" s="7">
-        <v>61.2</v>
+        <v>73.3</v>
       </c>
       <c r="E7" s="7">
         <v>52</v>
       </c>
-      <c r="F7" s="8">
-        <v>-0.5</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-0.9</v>
+      <c r="F7" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>21.92</v>
       </c>
       <c r="H7" s="9">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="I7" s="8">
-        <v>-51.4</v>
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="10">
+        <v>49.6</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K7" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M7" s="9">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="N7" s="8">
-        <v>-51.4</v>
+        <v>0.01</v>
+      </c>
+      <c r="N7" s="10">
+        <v>49.6</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P7" s="9">
-        <v>5.1700000000000003E-2</v>
+        <v>6.1699999999999998E-2</v>
       </c>
       <c r="Q7" s="9" t="s">
         <v>17</v>
@@ -1543,52 +1549,52 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>54.9</v>
+        <v>55.8</v>
       </c>
       <c r="C8" s="7">
-        <v>55.7</v>
+        <v>55.2</v>
       </c>
       <c r="D8" s="7">
-        <v>62.4</v>
+        <v>61.2</v>
       </c>
       <c r="E8" s="7">
-        <v>53.7</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.54</v>
+        <v>52</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-0.9</v>
       </c>
       <c r="H8" s="9">
-        <v>1.38E-2</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="I8" s="8">
+        <v>-51.4</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K8" s="9">
-        <v>4.4999999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M8" s="9">
-        <v>1.38E-2</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="N8" s="8">
+        <v>-51.4</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P8" s="9">
-        <v>4.4999999999999998E-2</v>
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="Q8" s="9" t="s">
         <v>17</v>
@@ -1596,37 +1602,37 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>59.6</v>
+        <v>54.9</v>
       </c>
       <c r="C9" s="7">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="D9" s="7">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="E9" s="7">
-        <v>52.4</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-3.6</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-6.1</v>
+        <v>53.7</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.54</v>
       </c>
       <c r="H9" s="9">
         <v>1.38E-2</v>
       </c>
-      <c r="I9" s="10">
-        <v>64.2</v>
+      <c r="I9" s="9">
+        <v>0</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K9" s="9">
-        <v>3.1199999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>17</v>
@@ -1634,14 +1640,14 @@
       <c r="M9" s="9">
         <v>1.38E-2</v>
       </c>
-      <c r="N9" s="10">
-        <v>64.2</v>
+      <c r="N9" s="9">
+        <v>0</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P9" s="9">
-        <v>3.1199999999999999E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q9" s="9" t="s">
         <v>17</v>
@@ -1649,52 +1655,52 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>54.5</v>
+        <v>59.6</v>
       </c>
       <c r="C10" s="7">
-        <v>59</v>
+        <v>55.4</v>
       </c>
       <c r="D10" s="7">
-        <v>63</v>
+        <v>60.5</v>
       </c>
       <c r="E10" s="7">
-        <v>54</v>
-      </c>
-      <c r="F10" s="10">
-        <v>5.8</v>
-      </c>
-      <c r="G10" s="10">
-        <v>10.9</v>
+        <v>52.4</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-3.6</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-6.1</v>
       </c>
       <c r="H10" s="9">
-        <v>8.3999999999999995E-3</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-8.01</v>
+        <v>1.38E-2</v>
+      </c>
+      <c r="I10" s="10">
+        <v>64.2</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K10" s="9">
-        <v>1.7500000000000002E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M10" s="9">
-        <v>8.3999999999999995E-3</v>
-      </c>
-      <c r="N10" s="8">
-        <v>-8.01</v>
+        <v>1.38E-2</v>
+      </c>
+      <c r="N10" s="10">
+        <v>64.2</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P10" s="9">
-        <v>1.7500000000000002E-2</v>
+        <v>3.1199999999999999E-2</v>
       </c>
       <c r="Q10" s="9" t="s">
         <v>17</v>
@@ -1702,52 +1708,52 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>58.5</v>
+        <v>54.5</v>
       </c>
       <c r="C11" s="7">
-        <v>53.2</v>
+        <v>59</v>
       </c>
       <c r="D11" s="7">
         <v>63</v>
       </c>
       <c r="E11" s="7">
-        <v>51.3</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-8.43</v>
+        <v>54</v>
+      </c>
+      <c r="F11" s="10">
+        <v>5.8</v>
+      </c>
+      <c r="G11" s="10">
+        <v>10.9</v>
       </c>
       <c r="H11" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="I11" s="8">
-        <v>-29.2</v>
+        <v>-8.01</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K11" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M11" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="N11" s="8">
-        <v>-29.2</v>
+        <v>-8.01</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P11" s="9">
-        <v>9.1000000000000004E-3</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="Q11" s="9" t="s">
         <v>17</v>
@@ -1755,243 +1761,243 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>52.4</v>
+        <v>58.5</v>
       </c>
       <c r="C12" s="7">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="D12" s="7">
-        <v>81.8</v>
+        <v>63</v>
       </c>
       <c r="E12" s="7">
-        <v>52</v>
-      </c>
-      <c r="F12" s="10">
-        <v>5.8</v>
-      </c>
-      <c r="G12" s="10">
-        <v>11.09</v>
+        <v>51.3</v>
+      </c>
+      <c r="F12" s="8">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-8.43</v>
       </c>
       <c r="H12" s="9">
-        <v>1.29E-2</v>
-      </c>
-      <c r="I12" s="10">
-        <v>120.6</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-29.2</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="9">
-        <v>5.4100000000000002E-2</v>
-      </c>
-      <c r="L12" s="10">
-        <v>1702</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M12" s="9">
-        <v>1.29E-2</v>
-      </c>
-      <c r="N12" s="10">
-        <v>120.6</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="N12" s="8">
+        <v>-29.2</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P12" s="9">
-        <v>5.4100000000000002E-2</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>1702</v>
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>51.4</v>
+        <v>52.4</v>
       </c>
       <c r="C13" s="7">
-        <v>52.3</v>
+        <v>58.1</v>
       </c>
       <c r="D13" s="7">
-        <v>54.9</v>
+        <v>81.8</v>
       </c>
       <c r="E13" s="7">
-        <v>48.35</v>
+        <v>52</v>
       </c>
       <c r="F13" s="10">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="G13" s="10">
-        <v>1.55</v>
+        <v>11.09</v>
       </c>
       <c r="H13" s="9">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-80.400000000000006</v>
+        <v>1.29E-2</v>
+      </c>
+      <c r="I13" s="10">
+        <v>120.6</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="9">
-        <v>4.1200000000000001E-2</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="L13" s="10">
-        <v>1273.3</v>
+        <v>1702</v>
       </c>
       <c r="M13" s="9">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-80.400000000000006</v>
+        <v>1.29E-2</v>
+      </c>
+      <c r="N13" s="10">
+        <v>120.6</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P13" s="9">
-        <v>4.1200000000000001E-2</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="Q13" s="10">
-        <v>1273.3</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>44.9</v>
+        <v>51.4</v>
       </c>
       <c r="C14" s="7">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
       <c r="D14" s="7">
-        <v>58</v>
+        <v>54.9</v>
       </c>
       <c r="E14" s="7">
-        <v>41.65</v>
+        <v>48.35</v>
       </c>
       <c r="F14" s="10">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="G14" s="10">
-        <v>13.44</v>
+        <v>1.55</v>
       </c>
       <c r="H14" s="9">
-        <v>2.98E-2</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>17</v>
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-80.400000000000006</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="9">
-        <v>3.5400000000000001E-2</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="L14" s="10">
-        <v>1079</v>
+        <v>1273.3</v>
       </c>
       <c r="M14" s="9">
-        <v>2.98E-2</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>17</v>
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="N14" s="8">
+        <v>-80.400000000000006</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P14" s="9">
-        <v>3.5400000000000001E-2</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="Q14" s="10">
-        <v>1079</v>
+        <v>1273.3</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="C15" s="7">
-        <v>45.4</v>
+        <v>51.5</v>
       </c>
       <c r="D15" s="7">
-        <v>48.6</v>
+        <v>58</v>
       </c>
       <c r="E15" s="7">
-        <v>42.65</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-2.6</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-5.42</v>
+        <v>41.65</v>
+      </c>
+      <c r="F15" s="10">
+        <v>6.1</v>
+      </c>
+      <c r="G15" s="10">
+        <v>13.44</v>
       </c>
       <c r="H15" s="9">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>-100</v>
+        <v>2.98E-2</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="L15" s="10">
-        <v>86.7</v>
+        <v>1079</v>
       </c>
       <c r="M15" s="9">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>-100</v>
+        <v>2.98E-2</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P15" s="9">
-        <v>5.5999999999999999E-3</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="Q15" s="10">
-        <v>86.7</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>54</v>
+        <v>47.5</v>
       </c>
       <c r="C16" s="7">
-        <v>48</v>
+        <v>45.4</v>
       </c>
       <c r="D16" s="7">
-        <v>55.4</v>
+        <v>48.6</v>
       </c>
       <c r="E16" s="7">
-        <v>45</v>
+        <v>42.65</v>
       </c>
       <c r="F16" s="8">
-        <v>-5.8</v>
+        <v>-2.6</v>
       </c>
       <c r="G16" s="8">
-        <v>-10.78</v>
+        <v>-5.42</v>
       </c>
       <c r="H16" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="8">
+        <v>-100</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>17</v>
@@ -2003,10 +2009,10 @@
         <v>86.7</v>
       </c>
       <c r="M16" s="9">
-        <v>5.5999999999999999E-3</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N16" s="8">
+        <v>-100</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>17</v>
@@ -2020,78 +2026,78 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C17" s="7">
-        <v>53.8</v>
+        <v>48</v>
       </c>
       <c r="D17" s="7">
-        <v>59.8</v>
+        <v>55.4</v>
       </c>
       <c r="E17" s="7">
-        <v>47.35</v>
+        <v>45</v>
       </c>
       <c r="F17" s="8">
-        <v>-4.0999999999999996</v>
+        <v>-5.8</v>
       </c>
       <c r="G17" s="8">
-        <v>-7.08</v>
+        <v>-10.78</v>
       </c>
       <c r="H17" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="8">
-        <v>-100</v>
+      <c r="J17" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K17" s="9">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>-100</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="L17" s="10">
+        <v>86.7</v>
       </c>
       <c r="M17" s="9">
-        <v>0</v>
+        <v>5.5999999999999999E-3</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="8">
-        <v>-100</v>
+      <c r="O17" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P17" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>-100</v>
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>86.7</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>59.1</v>
+        <v>58</v>
       </c>
       <c r="C18" s="7">
-        <v>57.9</v>
+        <v>53.8</v>
       </c>
       <c r="D18" s="7">
-        <v>63.8</v>
+        <v>59.8</v>
       </c>
       <c r="E18" s="7">
-        <v>55.8</v>
+        <v>47.35</v>
       </c>
       <c r="F18" s="8">
-        <v>-1</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="G18" s="8">
-        <v>-1.7</v>
+        <v>-7.08</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2099,14 +2105,14 @@
       <c r="I18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>17</v>
+      <c r="J18" s="8">
+        <v>-100</v>
       </c>
       <c r="K18" s="9">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="s">
-        <v>17</v>
+      <c r="L18" s="8">
+        <v>-100</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -2114,37 +2120,37 @@
       <c r="N18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O18" s="9" t="s">
-        <v>17</v>
+      <c r="O18" s="8">
+        <v>-100</v>
       </c>
       <c r="P18" s="9">
         <v>0</v>
       </c>
-      <c r="Q18" s="9" t="s">
-        <v>17</v>
+      <c r="Q18" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>67.2</v>
+        <v>59.1</v>
       </c>
       <c r="C19" s="7">
-        <v>58.9</v>
+        <v>57.9</v>
       </c>
       <c r="D19" s="7">
-        <v>67.2</v>
+        <v>63.8</v>
       </c>
       <c r="E19" s="7">
-        <v>50.1</v>
+        <v>55.8</v>
       </c>
       <c r="F19" s="8">
-        <v>-7.8</v>
+        <v>-1</v>
       </c>
       <c r="G19" s="8">
-        <v>-11.69</v>
+        <v>-1.7</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2179,25 +2185,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>89</v>
+        <v>67.2</v>
       </c>
       <c r="C20" s="7">
-        <v>66.7</v>
+        <v>58.9</v>
       </c>
       <c r="D20" s="7">
-        <v>93.9</v>
+        <v>67.2</v>
       </c>
       <c r="E20" s="7">
-        <v>63.3</v>
+        <v>50.1</v>
       </c>
       <c r="F20" s="8">
-        <v>-22.3</v>
+        <v>-7.8</v>
       </c>
       <c r="G20" s="8">
-        <v>-25.06</v>
+        <v>-11.69</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2232,25 +2238,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C21" s="7">
-        <v>89</v>
+        <v>66.7</v>
       </c>
       <c r="D21" s="7">
-        <v>100</v>
+        <v>93.9</v>
       </c>
       <c r="E21" s="7">
-        <v>58.1</v>
-      </c>
-      <c r="F21" s="10">
-        <v>31.5</v>
-      </c>
-      <c r="G21" s="10">
-        <v>54.78</v>
+        <v>63.3</v>
+      </c>
+      <c r="F21" s="8">
+        <v>-22.3</v>
+      </c>
+      <c r="G21" s="8">
+        <v>-25.06</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2285,25 +2291,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>35.200000000000003</v>
+        <v>60</v>
       </c>
       <c r="C22" s="7">
-        <v>57.5</v>
+        <v>89</v>
       </c>
       <c r="D22" s="7">
-        <v>59.7</v>
+        <v>100</v>
       </c>
       <c r="E22" s="7">
-        <v>35</v>
+        <v>58.1</v>
       </c>
       <c r="F22" s="10">
-        <v>22.4</v>
+        <v>31.5</v>
       </c>
       <c r="G22" s="10">
-        <v>63.82</v>
+        <v>54.78</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2338,25 +2344,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>37.549999999999997</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="C23" s="7">
-        <v>35.1</v>
+        <v>57.5</v>
       </c>
       <c r="D23" s="7">
-        <v>37.65</v>
+        <v>59.7</v>
       </c>
       <c r="E23" s="7">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="F23" s="8">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="G23" s="8">
-        <v>-6.15</v>
+        <v>35</v>
+      </c>
+      <c r="F23" s="10">
+        <v>22.4</v>
+      </c>
+      <c r="G23" s="10">
+        <v>63.82</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2391,25 +2397,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>43.45</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="C24" s="7">
-        <v>37.4</v>
+        <v>35.1</v>
       </c>
       <c r="D24" s="7">
-        <v>43.5</v>
+        <v>37.65</v>
       </c>
       <c r="E24" s="7">
-        <v>36.35</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="F24" s="8">
-        <v>-5.6</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="G24" s="8">
-        <v>-13.02</v>
+        <v>-6.15</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2421,7 +2427,7 @@
         <v>17</v>
       </c>
       <c r="K24" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="s">
         <v>17</v>
@@ -2436,7 +2442,7 @@
         <v>17</v>
       </c>
       <c r="P24" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="9" t="s">
         <v>17</v>
@@ -2444,25 +2450,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>37.5</v>
+        <v>43.45</v>
       </c>
       <c r="C25" s="7">
-        <v>43</v>
+        <v>37.4</v>
       </c>
       <c r="D25" s="7">
-        <v>46</v>
+        <v>43.5</v>
       </c>
       <c r="E25" s="7">
-        <v>37.1</v>
-      </c>
-      <c r="F25" s="10">
-        <v>5.6</v>
-      </c>
-      <c r="G25" s="10">
-        <v>14.97</v>
+        <v>36.35</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-5.6</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-13.02</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2497,25 +2503,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="C26" s="7">
-        <v>37.4</v>
+        <v>43</v>
       </c>
       <c r="D26" s="7">
-        <v>41.45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="7">
         <v>37.1</v>
       </c>
-      <c r="F26" s="8">
-        <v>-2.6</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-6.5</v>
+      <c r="F26" s="10">
+        <v>5.6</v>
+      </c>
+      <c r="G26" s="10">
+        <v>14.97</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2550,25 +2556,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="C27" s="7">
-        <v>40</v>
+        <v>37.4</v>
       </c>
       <c r="D27" s="7">
-        <v>45.8</v>
+        <v>41.45</v>
       </c>
       <c r="E27" s="7">
-        <v>37.049999999999997</v>
+        <v>37.1</v>
       </c>
       <c r="F27" s="8">
-        <v>-0.15</v>
+        <v>-2.6</v>
       </c>
       <c r="G27" s="8">
-        <v>-0.37</v>
+        <v>-6.5</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2603,31 +2609,31 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>42.8</v>
+        <v>39.6</v>
       </c>
       <c r="C28" s="7">
-        <v>40.15</v>
+        <v>40</v>
       </c>
       <c r="D28" s="7">
-        <v>43.6</v>
+        <v>45.8</v>
       </c>
       <c r="E28" s="7">
-        <v>37</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="F28" s="8">
-        <v>-2.85</v>
+        <v>-0.15</v>
       </c>
       <c r="G28" s="8">
-        <v>-6.63</v>
+        <v>-0.37</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
       </c>
-      <c r="I28" s="8">
-        <v>-100</v>
+      <c r="I28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>17</v>
@@ -2641,8 +2647,8 @@
       <c r="M28" s="9">
         <v>0</v>
       </c>
-      <c r="N28" s="8">
-        <v>-100</v>
+      <c r="N28" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>17</v>
@@ -2656,31 +2662,31 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>47.9</v>
+        <v>42.8</v>
       </c>
       <c r="C29" s="7">
-        <v>43</v>
+        <v>40.15</v>
       </c>
       <c r="D29" s="7">
-        <v>60.6</v>
+        <v>43.6</v>
       </c>
       <c r="E29" s="7">
-        <v>40.049999999999997</v>
+        <v>37</v>
       </c>
       <c r="F29" s="8">
-        <v>-4.9000000000000004</v>
+        <v>-2.85</v>
       </c>
       <c r="G29" s="8">
-        <v>-10.23</v>
+        <v>-6.63</v>
       </c>
       <c r="H29" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
+        <v>-100</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>17</v>
@@ -2692,10 +2698,10 @@
         <v>17</v>
       </c>
       <c r="M29" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>-100</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>17</v>
@@ -2709,28 +2715,28 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>45.2</v>
+        <v>47.9</v>
       </c>
       <c r="C30" s="7">
-        <v>47.9</v>
+        <v>43</v>
       </c>
       <c r="D30" s="7">
-        <v>52.7</v>
+        <v>60.6</v>
       </c>
       <c r="E30" s="7">
-        <v>43.8</v>
-      </c>
-      <c r="F30" s="10">
-        <v>2.75</v>
-      </c>
-      <c r="G30" s="10">
-        <v>6.09</v>
+        <v>40.049999999999997</v>
+      </c>
+      <c r="F30" s="8">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="G30" s="8">
+        <v>-10.23</v>
       </c>
       <c r="H30" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>17</v>
@@ -2739,13 +2745,13 @@
         <v>17</v>
       </c>
       <c r="K30" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L30" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M30" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>17</v>
@@ -2754,7 +2760,7 @@
         <v>17</v>
       </c>
       <c r="P30" s="9">
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q30" s="9" t="s">
         <v>17</v>
@@ -2762,25 +2768,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>37.5</v>
+        <v>45.2</v>
       </c>
       <c r="C31" s="7">
-        <v>45.15</v>
+        <v>47.9</v>
       </c>
       <c r="D31" s="7">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="E31" s="7">
-        <v>37.450000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="F31" s="10">
-        <v>7.1</v>
+        <v>2.75</v>
       </c>
       <c r="G31" s="10">
-        <v>18.66</v>
+        <v>6.09</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2815,25 +2821,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>30.55</v>
+        <v>37.5</v>
       </c>
       <c r="C32" s="7">
-        <v>38.049999999999997</v>
+        <v>45.15</v>
       </c>
       <c r="D32" s="7">
-        <v>39</v>
+        <v>52.8</v>
       </c>
       <c r="E32" s="7">
-        <v>29.9</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="F32" s="10">
-        <v>7.65</v>
+        <v>7.1</v>
       </c>
       <c r="G32" s="10">
-        <v>25.16</v>
+        <v>18.66</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2868,25 +2874,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>43.5</v>
+        <v>30.55</v>
       </c>
       <c r="C33" s="7">
-        <v>30.4</v>
+        <v>38.049999999999997</v>
       </c>
       <c r="D33" s="7">
-        <v>48.5</v>
+        <v>39</v>
       </c>
       <c r="E33" s="7">
-        <v>24.5</v>
-      </c>
-      <c r="F33" s="8">
-        <v>-14.05</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-31.61</v>
+        <v>29.9</v>
+      </c>
+      <c r="F33" s="10">
+        <v>7.65</v>
+      </c>
+      <c r="G33" s="10">
+        <v>25.16</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2921,25 +2927,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>41.9</v>
+        <v>43.5</v>
       </c>
       <c r="C34" s="7">
-        <v>44.45</v>
+        <v>30.4</v>
       </c>
       <c r="D34" s="7">
-        <v>48.85</v>
+        <v>48.5</v>
       </c>
       <c r="E34" s="7">
-        <v>38.75</v>
-      </c>
-      <c r="F34" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="G34" s="10">
-        <v>6.47</v>
+        <v>24.5</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-14.05</v>
+      </c>
+      <c r="G34" s="8">
+        <v>-31.61</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2974,25 +2980,25 @@
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>44.5</v>
+        <v>41.9</v>
       </c>
       <c r="C35" s="7">
-        <v>41.75</v>
+        <v>44.45</v>
       </c>
       <c r="D35" s="7">
-        <v>45.1</v>
+        <v>48.85</v>
       </c>
       <c r="E35" s="7">
-        <v>41.3</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-6.7</v>
+        <v>38.75</v>
+      </c>
+      <c r="F35" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="G35" s="10">
+        <v>6.47</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3027,25 +3033,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>49.5</v>
+        <v>44.5</v>
       </c>
       <c r="C36" s="7">
-        <v>44.75</v>
+        <v>41.75</v>
       </c>
       <c r="D36" s="7">
-        <v>49.5</v>
+        <v>45.1</v>
       </c>
       <c r="E36" s="7">
-        <v>36.85</v>
+        <v>41.3</v>
       </c>
       <c r="F36" s="8">
-        <v>-4.45</v>
+        <v>-3</v>
       </c>
       <c r="G36" s="8">
-        <v>-9.0399999999999991</v>
+        <v>-6.7</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3080,25 +3086,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="C37" s="7">
-        <v>49.2</v>
+        <v>44.75</v>
       </c>
       <c r="D37" s="7">
-        <v>53.9</v>
+        <v>49.5</v>
       </c>
       <c r="E37" s="7">
-        <v>47.75</v>
+        <v>36.85</v>
       </c>
       <c r="F37" s="8">
-        <v>-2.2999999999999998</v>
+        <v>-4.45</v>
       </c>
       <c r="G37" s="8">
-        <v>-4.47</v>
+        <v>-9.0399999999999991</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3133,25 +3139,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>64.7</v>
+        <v>51.5</v>
       </c>
       <c r="C38" s="7">
-        <v>51.5</v>
+        <v>49.2</v>
       </c>
       <c r="D38" s="7">
-        <v>65.8</v>
+        <v>53.9</v>
       </c>
       <c r="E38" s="7">
-        <v>50.5</v>
+        <v>47.75</v>
       </c>
       <c r="F38" s="8">
-        <v>-13.5</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="G38" s="8">
-        <v>-20.77</v>
+        <v>-4.47</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3186,25 +3192,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
-        <v>69.900000000000006</v>
+        <v>64.7</v>
       </c>
       <c r="C39" s="7">
-        <v>65</v>
+        <v>51.5</v>
       </c>
       <c r="D39" s="7">
-        <v>73.5</v>
+        <v>65.8</v>
       </c>
       <c r="E39" s="7">
-        <v>64.3</v>
+        <v>50.5</v>
       </c>
       <c r="F39" s="8">
-        <v>-4.3</v>
+        <v>-13.5</v>
       </c>
       <c r="G39" s="8">
-        <v>-6.2</v>
+        <v>-20.77</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3239,25 +3245,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>72</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="C40" s="7">
-        <v>69.3</v>
+        <v>65</v>
       </c>
       <c r="D40" s="7">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="E40" s="7">
-        <v>66.2</v>
+        <v>64.3</v>
       </c>
       <c r="F40" s="8">
-        <v>-2.7</v>
+        <v>-4.3</v>
       </c>
       <c r="G40" s="8">
-        <v>-3.75</v>
+        <v>-6.2</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3292,25 +3298,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>74.3</v>
+        <v>72</v>
       </c>
       <c r="C41" s="7">
-        <v>72</v>
+        <v>69.3</v>
       </c>
       <c r="D41" s="7">
-        <v>83.9</v>
+        <v>72.5</v>
       </c>
       <c r="E41" s="7">
-        <v>71</v>
+        <v>66.2</v>
       </c>
       <c r="F41" s="8">
-        <v>-1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="G41" s="8">
-        <v>-1.64</v>
+        <v>-3.75</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3345,25 +3351,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="C42" s="7">
-        <v>73.2</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7">
-        <v>77.900000000000006</v>
+        <v>83.9</v>
       </c>
       <c r="E42" s="7">
-        <v>72.599999999999994</v>
+        <v>71</v>
       </c>
       <c r="F42" s="8">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="G42" s="8">
-        <v>-1.35</v>
+        <v>-1.64</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3398,25 +3404,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>70.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="C43" s="7">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="D43" s="7">
-        <v>75.900000000000006</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="E43" s="7">
-        <v>63.4</v>
-      </c>
-      <c r="F43" s="10">
-        <v>3.6</v>
-      </c>
-      <c r="G43" s="10">
-        <v>5.0999999999999996</v>
+        <v>72.599999999999994</v>
+      </c>
+      <c r="F43" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G43" s="8">
+        <v>-1.35</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3451,25 +3457,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>74.099999999999994</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="C44" s="7">
-        <v>70.599999999999994</v>
+        <v>74.2</v>
       </c>
       <c r="D44" s="7">
-        <v>77.5</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="E44" s="7">
-        <v>70.5</v>
-      </c>
-      <c r="F44" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="G44" s="8">
-        <v>-4.47</v>
+        <v>63.4</v>
+      </c>
+      <c r="F44" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="G44" s="10">
+        <v>5.0999999999999996</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3504,25 +3510,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>76.5</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="C45" s="7">
-        <v>73.900000000000006</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="D45" s="7">
-        <v>77.8</v>
+        <v>77.5</v>
       </c>
       <c r="E45" s="7">
         <v>70.5</v>
       </c>
       <c r="F45" s="8">
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="G45" s="8">
-        <v>-2.12</v>
+        <v>-4.47</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3557,25 +3563,25 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>69</v>
+        <v>76.5</v>
       </c>
       <c r="C46" s="7">
-        <v>75.5</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="D46" s="7">
-        <v>80.900000000000006</v>
+        <v>77.8</v>
       </c>
       <c r="E46" s="7">
-        <v>69</v>
-      </c>
-      <c r="F46" s="10">
-        <v>6.9</v>
-      </c>
-      <c r="G46" s="10">
-        <v>10.06</v>
+        <v>70.5</v>
+      </c>
+      <c r="F46" s="8">
+        <v>-1.6</v>
+      </c>
+      <c r="G46" s="8">
+        <v>-2.12</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3610,25 +3616,25 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>62.9</v>
+        <v>69</v>
       </c>
       <c r="C47" s="7">
-        <v>68.599999999999994</v>
+        <v>75.5</v>
       </c>
       <c r="D47" s="7">
-        <v>70.900000000000006</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="E47" s="7">
-        <v>61.5</v>
+        <v>69</v>
       </c>
       <c r="F47" s="10">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="G47" s="10">
-        <v>9.76</v>
+        <v>10.06</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3663,25 +3669,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
       <c r="C48" s="7">
-        <v>62.5</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D48" s="7">
-        <v>66.5</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E48" s="7">
-        <v>59</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-3.4</v>
+        <v>61.5</v>
+      </c>
+      <c r="F48" s="10">
+        <v>6.1</v>
+      </c>
+      <c r="G48" s="10">
+        <v>9.76</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3716,25 +3722,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>56</v>
+        <v>65.8</v>
       </c>
       <c r="C49" s="7">
-        <v>64.7</v>
+        <v>62.5</v>
       </c>
       <c r="D49" s="7">
-        <v>66.400000000000006</v>
+        <v>66.5</v>
       </c>
       <c r="E49" s="7">
-        <v>54</v>
-      </c>
-      <c r="F49" s="10">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="G49" s="10">
-        <v>15.54</v>
+        <v>59</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-3.4</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3769,25 +3775,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>83.4</v>
+        <v>56</v>
       </c>
       <c r="C50" s="7">
-        <v>56</v>
+        <v>64.7</v>
       </c>
       <c r="D50" s="7">
-        <v>84.9</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="E50" s="7">
-        <v>53</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-22</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-28.21</v>
+        <v>54</v>
+      </c>
+      <c r="F50" s="10">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G50" s="10">
+        <v>15.54</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3822,25 +3828,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>84.6</v>
+        <v>83.4</v>
       </c>
       <c r="C51" s="7">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D51" s="7">
-        <v>84.6</v>
+        <v>84.9</v>
       </c>
       <c r="E51" s="7">
-        <v>72.900000000000006</v>
+        <v>53</v>
       </c>
       <c r="F51" s="8">
-        <v>-6</v>
+        <v>-22</v>
       </c>
       <c r="G51" s="8">
-        <v>-7.14</v>
+        <v>-28.21</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3875,25 +3881,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>89</v>
+        <v>84.6</v>
       </c>
       <c r="C52" s="7">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D52" s="7">
-        <v>90.5</v>
+        <v>84.6</v>
       </c>
       <c r="E52" s="7">
-        <v>82.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="F52" s="8">
-        <v>-4.5</v>
+        <v>-6</v>
       </c>
       <c r="G52" s="8">
-        <v>-5.08</v>
+        <v>-7.14</v>
       </c>
       <c r="H52" s="9">
         <v>0</v>
@@ -3928,25 +3934,25 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C53" s="7">
-        <v>88.5</v>
+        <v>84</v>
       </c>
       <c r="D53" s="7">
-        <v>103</v>
+        <v>90.5</v>
       </c>
       <c r="E53" s="7">
-        <v>87.5</v>
+        <v>82.7</v>
       </c>
       <c r="F53" s="8">
-        <v>-14</v>
+        <v>-4.5</v>
       </c>
       <c r="G53" s="8">
-        <v>-13.66</v>
+        <v>-5.08</v>
       </c>
       <c r="H53" s="9">
         <v>0</v>
@@ -3981,25 +3987,25 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>113.5</v>
+        <v>102</v>
       </c>
       <c r="C54" s="7">
-        <v>102.5</v>
+        <v>88.5</v>
       </c>
       <c r="D54" s="7">
-        <v>113.5</v>
+        <v>103</v>
       </c>
       <c r="E54" s="7">
-        <v>97.6</v>
+        <v>87.5</v>
       </c>
       <c r="F54" s="8">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="G54" s="8">
-        <v>-8.07</v>
+        <v>-13.66</v>
       </c>
       <c r="H54" s="9">
         <v>0</v>
@@ -4034,25 +4040,25 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>115</v>
+        <v>113.5</v>
       </c>
       <c r="C55" s="7">
-        <v>111.5</v>
+        <v>102.5</v>
       </c>
       <c r="D55" s="7">
-        <v>132.5</v>
+        <v>113.5</v>
       </c>
       <c r="E55" s="7">
-        <v>108.5</v>
+        <v>97.6</v>
       </c>
       <c r="F55" s="8">
-        <v>-2.5</v>
+        <v>-9</v>
       </c>
       <c r="G55" s="8">
-        <v>-2.19</v>
+        <v>-8.07</v>
       </c>
       <c r="H55" s="9">
         <v>0</v>
@@ -4087,25 +4093,25 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C56" s="7">
-        <v>114</v>
+        <v>111.5</v>
       </c>
       <c r="D56" s="7">
-        <v>120</v>
+        <v>132.5</v>
       </c>
       <c r="E56" s="7">
-        <v>97.6</v>
-      </c>
-      <c r="F56" s="10">
-        <v>11</v>
-      </c>
-      <c r="G56" s="10">
-        <v>10.68</v>
+        <v>108.5</v>
+      </c>
+      <c r="F56" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G56" s="8">
+        <v>-2.19</v>
       </c>
       <c r="H56" s="9">
         <v>0</v>
@@ -4140,25 +4146,25 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C57" s="7">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D57" s="7">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E57" s="7">
-        <v>79.099999999999994</v>
+        <v>97.6</v>
       </c>
       <c r="F57" s="10">
-        <v>19.3</v>
+        <v>11</v>
       </c>
       <c r="G57" s="10">
-        <v>23.06</v>
+        <v>10.68</v>
       </c>
       <c r="H57" s="9">
         <v>0</v>
@@ -4193,25 +4199,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>86.5</v>
+        <v>83</v>
       </c>
       <c r="C58" s="7">
-        <v>83.7</v>
+        <v>103</v>
       </c>
       <c r="D58" s="7">
-        <v>87.3</v>
+        <v>115</v>
       </c>
       <c r="E58" s="7">
-        <v>78.3</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-3.79</v>
+        <v>79.099999999999994</v>
+      </c>
+      <c r="F58" s="10">
+        <v>19.3</v>
+      </c>
+      <c r="G58" s="10">
+        <v>23.06</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4246,25 +4252,25 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>75.099999999999994</v>
+        <v>86.5</v>
       </c>
       <c r="C59" s="7">
-        <v>87</v>
+        <v>83.7</v>
       </c>
       <c r="D59" s="7">
-        <v>90.5</v>
+        <v>87.3</v>
       </c>
       <c r="E59" s="7">
-        <v>72.2</v>
-      </c>
-      <c r="F59" s="10">
-        <v>11.3</v>
-      </c>
-      <c r="G59" s="10">
-        <v>14.93</v>
+        <v>78.3</v>
+      </c>
+      <c r="F59" s="8">
+        <v>-3.3</v>
+      </c>
+      <c r="G59" s="8">
+        <v>-3.79</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4299,25 +4305,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
-        <v>84</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="C60" s="7">
-        <v>75.7</v>
+        <v>87</v>
       </c>
       <c r="D60" s="7">
-        <v>84</v>
+        <v>90.5</v>
       </c>
       <c r="E60" s="7">
-        <v>73.5</v>
-      </c>
-      <c r="F60" s="8">
-        <v>-8.4</v>
-      </c>
-      <c r="G60" s="8">
-        <v>-9.99</v>
+        <v>72.2</v>
+      </c>
+      <c r="F60" s="10">
+        <v>11.3</v>
+      </c>
+      <c r="G60" s="10">
+        <v>14.93</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4352,25 +4358,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C61" s="7">
-        <v>84.1</v>
+        <v>75.7</v>
       </c>
       <c r="D61" s="7">
-        <v>89.7</v>
+        <v>84</v>
       </c>
       <c r="E61" s="7">
-        <v>81.400000000000006</v>
+        <v>73.5</v>
       </c>
       <c r="F61" s="8">
-        <v>-3.2</v>
+        <v>-8.4</v>
       </c>
       <c r="G61" s="8">
-        <v>-3.67</v>
+        <v>-9.99</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4405,25 +4411,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C62" s="7">
-        <v>87.3</v>
+        <v>84.1</v>
       </c>
       <c r="D62" s="7">
-        <v>101.5</v>
+        <v>89.7</v>
       </c>
       <c r="E62" s="7">
-        <v>81</v>
-      </c>
-      <c r="F62" s="10">
-        <v>15.3</v>
-      </c>
-      <c r="G62" s="10">
-        <v>21.25</v>
+        <v>81.400000000000006</v>
+      </c>
+      <c r="F62" s="8">
+        <v>-3.2</v>
+      </c>
+      <c r="G62" s="8">
+        <v>-3.67</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4458,25 +4464,25 @@
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>17</v>
+        <v>43009</v>
+      </c>
+      <c r="B63" s="7">
+        <v>83</v>
+      </c>
+      <c r="C63" s="7">
+        <v>87.3</v>
+      </c>
+      <c r="D63" s="7">
+        <v>101.5</v>
+      </c>
+      <c r="E63" s="7">
+        <v>81</v>
+      </c>
+      <c r="F63" s="10">
+        <v>15.3</v>
+      </c>
+      <c r="G63" s="10">
+        <v>21.25</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4511,7 +4517,7 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>17</v>
@@ -4564,7 +4570,7 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>17</v>
@@ -4617,7 +4623,7 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>17</v>
@@ -4670,7 +4676,7 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>17</v>
@@ -4723,7 +4729,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4776,7 +4782,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4829,7 +4835,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4882,7 +4888,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4935,7 +4941,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4988,7 +4994,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5041,7 +5047,7 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5094,7 +5100,7 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5147,7 +5153,7 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5200,7 +5206,7 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5253,7 +5259,7 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5306,7 +5312,7 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5359,7 +5365,7 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5465,7 +5471,7 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5518,7 +5524,7 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>17</v>
@@ -5571,7 +5577,7 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>17</v>
@@ -5624,7 +5630,7 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>17</v>
@@ -5677,7 +5683,7 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>17</v>
@@ -5730,7 +5736,7 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>17</v>
@@ -5783,7 +5789,7 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5836,54 +5842,107 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89" s="9">
+        <v>0</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M89" s="9">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P89" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
         <v>42186</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H89" s="9">
-        <v>0</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K89" s="9">
-        <v>0</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M89" s="9">
-        <v>0</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P89" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="9" t="s">
+      <c r="B90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" s="9">
+        <v>0</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M90" s="9">
+        <v>0</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5902,7 +5961,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>